--- a/output/graficos_dimensiones/comunal_s_isapre_a_2022_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_s_isapre_a_2022_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:03</t>
+    <t xml:space="preserve">2026-09-09 22:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_s_isapre_a_2022_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_s_isapre_a_2022_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:56</t>
+    <t xml:space="preserve">2026-09-18 10:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_s_isapre_a_2022_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_s_isapre_a_2022_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:20</t>
+    <t xml:space="preserve">2026-09-23 12:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -863,7 +863,9 @@
       <c r="C21" s="2" t="n">
         <v>16206</v>
       </c>
-      <c r="D21" s="2"/>
+      <c r="D21" s="2" t="n">
+        <v>2022</v>
+      </c>
       <c r="E21" s="2"/>
     </row>
     <row r="22">
@@ -876,7 +878,9 @@
       <c r="C22" s="2" t="n">
         <v>16303</v>
       </c>
-      <c r="D22" s="2"/>
+      <c r="D22" s="2" t="n">
+        <v>2022</v>
+      </c>
       <c r="E22" s="2"/>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_s_isapre_a_2022_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_s_isapre_a_2022_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:23</t>
+    <t xml:space="preserve">2026-10-02 14:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_s_isapre_a_2022_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_s_isapre_a_2022_nuble.xlsx
@@ -93,7 +93,7 @@
     <t xml:space="preserve">Ninhue</t>
   </si>
   <si>
-    <t xml:space="preserve">Ranquil</t>
+    <t xml:space="preserve">Ránquil</t>
   </si>
   <si>
     <t xml:space="preserve">Ñiquén</t>
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:09</t>
+    <t xml:space="preserve">2026-10-04 08:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_s_isapre_a_2022_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_s_isapre_a_2022_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:42</t>
+    <t xml:space="preserve">2026-10-05 09:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
